--- a/zwt-finance-system/backend/app/assets/templates/Salary-Advance-Template.xlsx
+++ b/zwt-finance-system/backend/app/assets/templates/Salary-Advance-Template.xlsx
@@ -8687,16 +8687,16 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col width="5.63333333333333" customWidth="1" style="54" min="1" max="1"/>
-    <col width="3.3" customWidth="1" style="54" min="2" max="2"/>
+    <col width="6.88333333333333" customWidth="1" style="54" min="2" max="2"/>
     <col width="6.88333333333333" customWidth="1" style="54" min="3" max="3"/>
     <col width="6.88333333333333" customWidth="1" style="54" min="4" max="4"/>
-    <col width="10.8" customWidth="1" style="54" min="5" max="5"/>
+    <col width="6.8" customWidth="1" style="54" min="5" max="5"/>
     <col width="6.88333333333333" customWidth="1" style="54" min="6" max="6"/>
     <col width="6.88333333333333" customWidth="1" style="54" min="7" max="7"/>
     <col width="6.88333333333333" customWidth="1" style="54" min="8" max="8"/>
     <col width="6.88333333333333" customWidth="1" style="54" min="9" max="9"/>
     <col width="5.8" customWidth="1" style="54" min="10" max="10"/>
-    <col width="11.55" customWidth="1" style="54" min="11" max="11"/>
+    <col width="11.96666666666666" customWidth="1" style="54" min="11" max="11"/>
     <col width="8.1" customWidth="1" style="54" min="12" max="12"/>
   </cols>
   <sheetData>

--- a/zwt-finance-system/backend/app/assets/templates/Salary-Advance-Template.xlsx
+++ b/zwt-finance-system/backend/app/assets/templates/Salary-Advance-Template.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="22103" windowHeight="9780" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="使用说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="导入数据模板" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="当前记录" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="表单模板" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="字段映射" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="签名配置" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入数据模板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前记录" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表单模板" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段映射" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="签名配置" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1294,7 +1294,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>0</col>
@@ -1312,24 +1312,24 @@
       <nvPicPr>
         <cNvPr id="3" name="图片 8" descr="ZWT彩色PNG"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="114935" y="69215"/>
           <a:ext cx="806450" cy="735330"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -8687,17 +8687,17 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col width="5.63333333333333" customWidth="1" style="54" min="1" max="1"/>
-    <col width="6.88333333333333" customWidth="1" style="54" min="2" max="2"/>
+    <col width="3.2" customWidth="1" style="54" min="2" max="2"/>
     <col width="6.88333333333333" customWidth="1" style="54" min="3" max="3"/>
     <col width="6.88333333333333" customWidth="1" style="54" min="4" max="4"/>
     <col width="6.8" customWidth="1" style="54" min="5" max="5"/>
-    <col width="6.88333333333333" customWidth="1" style="54" min="6" max="6"/>
+    <col width="5.2" customWidth="1" style="54" min="6" max="6"/>
     <col width="6.88333333333333" customWidth="1" style="54" min="7" max="7"/>
     <col width="6.88333333333333" customWidth="1" style="54" min="8" max="8"/>
     <col width="6.88333333333333" customWidth="1" style="54" min="9" max="9"/>
-    <col width="5.8" customWidth="1" style="54" min="10" max="10"/>
-    <col width="11.96666666666666" customWidth="1" style="54" min="11" max="11"/>
-    <col width="8.1" customWidth="1" style="54" min="12" max="12"/>
+    <col width="4.8" customWidth="1" style="54" min="10" max="10"/>
+    <col width="15.5" customWidth="1" style="54" min="11" max="11"/>
+    <col width="10.9333333333333" customWidth="1" style="54" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1" s="54">
@@ -8815,7 +8815,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="31.5" customHeight="1" s="54">
+    <row r="9" ht="22" customHeight="1" s="54">
       <c r="A9" s="11" t="n"/>
       <c r="B9" s="11" t="n"/>
       <c r="C9" s="11" t="n"/>

--- a/zwt-finance-system/backend/app/assets/templates/Salary-Advance-Template.xlsx
+++ b/zwt-finance-system/backend/app/assets/templates/Salary-Advance-Template.xlsx
@@ -9190,7 +9190,7 @@
       <c r="E37" s="13" t="n"/>
       <c r="F37" s="13" t="n"/>
       <c r="G37" s="13" t="n"/>
-      <c r="H37" s="24">
+      <c r="H37" s="26">
         <f>"( "&amp;当前记录!$B$19&amp;" )"</f>
         <v/>
       </c>
@@ -9335,7 +9335,7 @@
       <c r="E47" s="13" t="n"/>
       <c r="F47" s="13" t="n"/>
       <c r="G47" s="13" t="n"/>
-      <c r="H47" s="24">
+      <c r="H47" s="26">
         <f>"( "&amp;当前记录!$B$22&amp;" )"</f>
         <v/>
       </c>
@@ -9393,8 +9393,10 @@
     <mergeCell ref="A50:L50"/>
     <mergeCell ref="K44:L46"/>
     <mergeCell ref="A5:L5"/>
+    <mergeCell ref="H37:J37"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="A14:L14"/>
+    <mergeCell ref="H47:J47"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="K26:L28"/>
     <mergeCell ref="F17:G17"/>
@@ -9407,12 +9409,10 @@
     <mergeCell ref="A40:L40"/>
     <mergeCell ref="J48:L48"/>
     <mergeCell ref="I8:J8"/>
-    <mergeCell ref="H37:L37"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="H22:L22"/>
     <mergeCell ref="C8:D8"/>
-    <mergeCell ref="H47:L47"/>
     <mergeCell ref="D10:L10"/>
     <mergeCell ref="J38:L38"/>
     <mergeCell ref="A15:L15"/>
